--- a/static/bh_import_template.xlsx
+++ b/static/bh_import_template.xlsx
@@ -5602,8 +5602,8 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="輸入錯誤" error="必須填寫 R、D、M 或 P（Prism）" type="list">
-      <formula1>"R,D,M,P"</formula1>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="輸入錯誤" error="必須填寫 R、D、M、P（Prism）或 V（D1影音）" type="list">
+      <formula1>"R,D,M,P,V"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="輸入無效" error="請選擇清單中的項目" promptTitle="選擇轉換定義" prompt="請從選單選擇轉換定義" type="list">
       <formula1>"CompleteCheckout,AddToCart,ViewContent,Checkout,Bookmark,Search,CompleteRegistration"</formula1>

--- a/static/bh_import_template.xlsx
+++ b/static/bh_import_template.xlsx
@@ -86,13 +86,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -621,14 +622,62 @@
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="B5" s="3" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>233-688-3595</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prism 廣告主（範例）</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="B6" s="3" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>CPM_MundoPixarExperience</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D1 影音帳戶（範例）</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" ht="14.25" customHeight="1">
       <c r="B7" s="3" t="n"/>

--- a/static/bh_import_template.xlsx
+++ b/static/bh_import_template.xlsx
@@ -463,7 +463,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="7.19921875" bestFit="1" customWidth="1" style="2" min="1" max="1"/>
-    <col width="10.796875" customWidth="1" style="2" min="2" max="2"/>
+    <col width="30" customWidth="1" style="2" min="2" max="2"/>
     <col width="20.19921875" bestFit="1" customWidth="1" style="2" min="3" max="3"/>
     <col width="10.59765625" bestFit="1" customWidth="1" style="2" min="4" max="4"/>
     <col width="15.3984375" bestFit="1" customWidth="1" style="2" min="5" max="6"/>
@@ -481,7 +481,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>AccID</t>
+          <t>AccID（MGID 填 API ID）</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
